--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cath\Desktop\PCB Projects\MiniLatte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94A98F77-5D24-4BD4-B6F8-0D358525FAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134D93BC-B3BD-463A-8F24-5585E0DEEF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{2BCEBE50-9A21-4E77-B4D3-345F262EF366}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2BCEBE50-9A21-4E77-B4D3-345F262EF366}"/>
   </bookViews>
   <sheets>
     <sheet name="hdmi" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="DP alt" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
   <si>
     <t>hdmi2</t>
   </si>
@@ -65,6 +65,15 @@
   </si>
   <si>
     <t>hdmi1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dl alt </t>
+  </si>
+  <si>
+    <t>rx2</t>
+  </si>
+  <si>
+    <t>rx1</t>
   </si>
 </sst>
 </file>
@@ -649,9 +658,129 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2BF11B-0D77-4805-838E-EAE70D1DAECC}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>41.49</v>
+      </c>
+      <c r="C3">
+        <v>44.26</v>
+      </c>
+      <c r="D3">
+        <v>37.409999999999997</v>
+      </c>
+      <c r="E3">
+        <v>45.85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>6.56</v>
+      </c>
+      <c r="C4">
+        <v>6.89</v>
+      </c>
+      <c r="D4">
+        <v>7.14</v>
+      </c>
+      <c r="E4">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>14.3</v>
+      </c>
+      <c r="C5">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="D5">
+        <v>4.7</v>
+      </c>
+      <c r="E5">
+        <v>17.02</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <f>SUM(B3:B5)</f>
+        <v>62.350000000000009</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:E6" si="0">SUM(C3:C5)</f>
+        <v>56.17</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>49.25</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>69.320000000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <f>E6-B6</f>
+        <v>6.9699999999999989</v>
+      </c>
+      <c r="C7">
+        <f>E6-C6</f>
+        <v>13.150000000000006</v>
+      </c>
+      <c r="D7">
+        <f>E6-D6</f>
+        <v>20.070000000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <f>B3+B7</f>
+        <v>48.46</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ref="C8:D8" si="1">C3+C7</f>
+        <v>57.410000000000004</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>57.480000000000004</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>